--- a/dev/StructureDefinition-bc-availability-extension.xlsx
+++ b/dev/StructureDefinition-bc-availability-extension.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-23T20:38:35+00:00</t>
+    <t>2026-01-23T00:06:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1250,7 +1250,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="5" hidden="true">
+    <row r="5">
       <c r="A5" t="s" s="2">
         <v>96</v>
       </c>
@@ -1355,7 +1355,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="6" hidden="true">
+    <row r="6">
       <c r="A6" t="s" s="2">
         <v>102</v>
       </c>
@@ -1460,7 +1460,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="7" hidden="true">
+    <row r="7">
       <c r="A7" t="s" s="2">
         <v>107</v>
       </c>
@@ -1876,7 +1876,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="11" hidden="true">
+    <row r="11">
       <c r="A11" t="s" s="2">
         <v>121</v>
       </c>
@@ -1979,7 +1979,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="12" hidden="true">
+    <row r="12">
       <c r="A12" t="s" s="2">
         <v>128</v>
       </c>
@@ -2084,7 +2084,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="13" hidden="true">
+    <row r="13">
       <c r="A13" t="s" s="2">
         <v>133</v>
       </c>
@@ -2189,7 +2189,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="14" hidden="true">
+    <row r="14">
       <c r="A14" t="s" s="2">
         <v>138</v>
       </c>
@@ -2504,12 +2504,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AK16">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
